--- a/data/qa/prospect_to_cash/shipment.xlsx
+++ b/data/qa/prospect_to_cash/shipment.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,126 +426,126 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:X7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>module</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>field</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>intent</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>sub_intent</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>canonical_question</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>answer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>synonyms</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>route</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>source_reference</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>source_section</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>site_scope</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>security_scope</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>approval_status</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>approved_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>effective_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>last_reviewed_date</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
@@ -542,7 +554,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QA-0017</t>
+          <t>KB-0127</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -552,50 +564,38 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Shipment</t>
+          <t>Fulfillment and Shipment Module</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Shipping</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Shipments</t>
-        </is>
-      </c>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HELP_GENERIC</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>definition</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>What is a Shipment?</t>
+          <t>What does shipment mean in the fulfillment process?</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>A Shipment is the physical delivery of ordered goods to the customer, created from a released Customer Order and used to record what was actually shipped.</t>
+          <t>Shipment is the fulfillment of a specific customer order line or release quantity from a shipping site. Order entry, reservation or supply, picking, shipment processing, and shipment confirmation are separate checkpoints in this process.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>shipment,delivery</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>delivery,dispatch</t>
-        </is>
-      </c>
+          <t>shipment, fulfillment, order shipping, Shipping Processing Orders, Ship Confirmation</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>FAST_QA</t>
@@ -603,18 +603,16 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>PTC Training Guide</t>
+          <t>shipment.md</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>8.1</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
+          <t>Fulfillment and Shipment Module &gt; What shipment means</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -627,10 +625,14 @@
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="V2" t="b">
@@ -638,10 +640,500 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0128</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>What are the different routes supported for shipping customer orders?</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Infor supports more than one route for shipping customer orders, including the Available to Ship Report plus Shipping Processing Orders, order pick lists, and shipment-based confirmation. You can choose the procedure your site uses.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>shipment, fulfillment, Shipping Processing Orders, order pick lists</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>shipment.md</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module &gt; What shipment means</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0129</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>What should I check before shipping an order?</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Before shipping an order, confirm the order is eligible to ship, identify the shipping site, warehouse, item, U/M, and requested or due date, and check customer and order Credit Hold, letter-of-credit rules, availability, and any lot/serial or reservation requirements.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>order eligibility, credit hold, available to ship, reservation requirements</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>shipment.md</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module &gt; Standard fulfillment checklist</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0130</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>HELP_FIELD</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>What does the Ship Partial option control in the shipment process?</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>The Ship Partial option controls whether the Available to Ship Report lists an order with only some lines ready; it does not by itself authorize a partial quantity of a line.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Ship Partial, partial shipment, Available to Ship Report, order lines</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>shipment.md</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module &gt; Partial shipment and backorder</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0131</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>How can I determine what was shipped and what remains open on an order?</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Determine what actually shipped and what remains open from order and shipment data. Do not promise that a remainder will automatically create a new shipment.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>order, shipment data, remaining quantity, open</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>shipment.md</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module &gt; Partial shipment and backorder</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0132</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROSPECT_TO_CASH</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HELP_PROCESS</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>What should I check if a shipment cannot post?</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Check the exact error, customer or order holds, line status, site or warehouse, inventory and reservation, serial or lot details, credit or letter-of-credit checks, ship-to, and required logistics fields. Escalate with the order, line, site, and error message rather than altering credit or inventory settings blindly.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>shipment, cannot post, troubleshooting, order holds, inventory</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>FAST_QA</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>shipment.md</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Fulfillment and Shipment Module &gt; Troubleshooting a shipment that cannot post</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>ALL</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>AUTO-DERIVED from knowledge base — pending SME review</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
         <is>
           <t>en</t>
         </is>
@@ -658,39 +1150,579 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>qa_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>variation_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>question_variation</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>KB-0127</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>What is shipment in SyteLine?</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>KB-0127</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Can you explain what shipment means?</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KB-0127</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>How is shipment defined in the system?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KB-0128</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>What shipping procedures are available?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KB-0128</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>How can I process shipments?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KB-0128</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>What are the options for shipping orders?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KB-0129</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>What needs to be verified before shipping?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>KB-0129</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How do I check if an order is ready to ship?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KB-0129</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>What are the pre-shipment checks?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KB-0130</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>How does Ship Partial affect my shipments?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>KB-0130</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>What happens if I use the Ship Partial option?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-0130</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Does Ship Partial let me ship part of a line?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KB-0131</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>How do I check what still needs to ship?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KB-0131</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Where can I see shipped vs open quantities?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KB-0131</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>How do I know what's left to ship on an order?</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>KB-0132</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Why can't my shipment post?</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KB-0132</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V2</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>What do I do if a shipment won't confirm?</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KB-0132</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>How do I troubleshoot a shipment that can't ship?</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>auto_derived</t>
+        </is>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
